--- a/tables/supplement_table_mouse_2.xlsx
+++ b/tables/supplement_table_mouse_2.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - Per-organ x group" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 - Per-organ x age" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -81,6 +82,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5755,4 +5759,212 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>accession</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>version_snapshot</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>derived_path_in_repo</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Bellenguez 2022 AD GWAS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Bellenguez et al. Nat Genet 2022</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>GCST90027158</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/gwas/studies/GCST90027158</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2022-04 (build GRCh38)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>data/gwas/Bellenguez2022_AD_withN.tsv.gz (gitignored)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Ncase ≈ 90k, Ntotal ≈ 788k; converted with `gsmap format_sumstats`</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>CMap-projected multi-age atlas</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Supplementary Table Mouse 1</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>data/age_merged/age_all_organs_all_traits.h5ad (gitignored, 5.6 GB)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>126 (organ × age) samples, 809,284 spots</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>gsMap quick_mode</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Liu et al. Nature Methods 2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>v1.x</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/JianYang-Lab/gsMap</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>commit pinned in env</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>models/gsmap_age_output/{sample}/spatial_ldsc/{sample}_AD.csv.gz (gitignored)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Per-spot AD S-LDSC χ² → p_AD column</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Per-organ summary CSVs</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>This work</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>results/age_organ_summary_per_age.csv + results/age_organ_summary_per_group.csv + results/age_overall_summary.csv</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Pre-aggregated by tables/build_supp_table_mouse_2.py header snippet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>